--- a/output/training_result_databaru/rules_training_filtered_70_30.xlsx
+++ b/output/training_result_databaru/rules_training_filtered_70_30.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">

--- a/output/training_result_databaru/rules_training_filtered_70_30.xlsx
+++ b/output/training_result_databaru/rules_training_filtered_70_30.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>kategori_rule</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>jenis_rule</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>jenis_rule_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -573,6 +583,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -639,6 +659,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -705,6 +735,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -771,6 +811,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -837,6 +887,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -903,6 +963,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -969,6 +1039,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1035,6 +1115,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1101,6 +1191,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1167,11 +1267,21 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1233,6 +1343,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1299,6 +1419,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1365,11 +1495,21 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozenset({'produk_night cream brightening', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1431,6 +1571,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1497,6 +1647,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1563,6 +1723,16 @@
           <t>Strong Pattern</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1629,6 +1799,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1695,6 +1875,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1761,6 +1951,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1827,6 +2027,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1893,6 +2103,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1959,6 +2179,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>produk_operator</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Produk × Operator</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2025,6 +2255,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2091,6 +2331,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2157,6 +2407,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2223,6 +2483,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2289,6 +2559,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2355,6 +2635,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2421,6 +2711,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2487,6 +2787,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2553,6 +2863,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2619,6 +2939,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2685,6 +3015,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2751,6 +3091,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2817,6 +3167,16 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>produk_waktu</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Produk × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2883,11 +3243,21 @@
           <t>Moderate Pattern</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>operator_waktu</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Operator × Waktu</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2947,6 +3317,16 @@
       <c r="R38" t="inlineStr">
         <is>
           <t>Moderate Pattern</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>produk_operator_waktu</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Produk × Operator × Waktu</t>
         </is>
       </c>
     </row>

--- a/output/training_result_databaru/rules_training_filtered_70_30.xlsx
+++ b/output/training_result_databaru/rules_training_filtered_70_30.xlsx
@@ -1433,7 +1433,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_serum brightening glowing'})</t>
+          <t>frozenset({'produk_serum brightening glowing', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1737,7 +1737,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_radian brightening ultimate'})</t>
+          <t>frozenset({'produk_radian brightening ultimate', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3029,7 +3029,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3257,7 +3257,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_facial wash oily acne 110 ml new'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
